--- a/01_cafe_photo/cafe_photo_metadata.xlsx
+++ b/01_cafe_photo/cafe_photo_metadata.xlsx
@@ -351,7 +351,7 @@
     </x:row>
     <x:row r="2" ht="72" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>IMG_002934.png</x:v>
+        <x:v>IMG_002934.jpg</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
         <x:v>44726.60564814815</x:v>
@@ -379,7 +379,7 @@
     </x:row>
     <x:row r="3" ht="72" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>IMG_002935.png</x:v>
+        <x:v>IMG_002935.jpg</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
         <x:v>44726.60603009259</x:v>
@@ -407,7 +407,7 @@
     </x:row>
     <x:row r="4" ht="72" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>IMG_002937.png</x:v>
+        <x:v>IMG_002937.jpg</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
         <x:v>44726.607083333336</x:v>
@@ -435,7 +435,7 @@
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>IMG_002938.png</x:v>
+        <x:v>IMG_002938.jpg</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
         <x:v>44726.60767361111</x:v>
@@ -463,7 +463,7 @@
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
       <x:c r="A6" s="11" t="str">
-        <x:v>IMG_002941.png</x:v>
+        <x:v>IMG_002941.jpg</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
         <x:v>44726.61002314815</x:v>
@@ -491,7 +491,7 @@
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
       <x:c r="A7" s="11" t="str">
-        <x:v>IMG_007452.png</x:v>
+        <x:v>IMG_007452.jpg</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
         <x:v>45492.672418981485</x:v>
@@ -519,7 +519,7 @@
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>IMG_007454.png</x:v>
+        <x:v>IMG_007454.jpg</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
         <x:v>45492.67371527778</x:v>
@@ -547,7 +547,7 @@
     </x:row>
     <x:row r="9" ht="72" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>IMG_007457.png</x:v>
+        <x:v>IMG_007457.jpg</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
         <x:v>45492.67618055556</x:v>
@@ -575,7 +575,7 @@
     </x:row>
     <x:row r="10" ht="72" customHeight="1">
       <x:c r="A10" s="11" t="str">
-        <x:v>IMG_012216.png</x:v>
+        <x:v>IMG_012216.jpg</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
         <x:v>46270.7827662037</x:v>
@@ -603,7 +603,7 @@
     </x:row>
     <x:row r="11" ht="72" customHeight="1">
       <x:c r="A11" s="11" t="str">
-        <x:v>IMG_012218.png</x:v>
+        <x:v>IMG_012218.jpg</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
         <x:v>46270.78375</x:v>
